--- a/data/trans_dic/P15D$ingresado-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P15D$ingresado-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 36,17</t>
+          <t>6,21; 38,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 15,65</t>
+          <t>2,9; 15,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,03</t>
+          <t>0,0; 13,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,25</t>
+          <t>0,0; 23,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,9</t>
+          <t>0,0; 26,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,68</t>
+          <t>0,0; 60,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,68; 29,04</t>
+          <t>4,76; 31,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,1; 14,95</t>
+          <t>3,12; 14,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,11</t>
+          <t>1,53; 13,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,67</t>
+          <t>0,0; 44,13</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 28,68</t>
+          <t>2,86; 30,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,43</t>
+          <t>1,19; 10,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 17,71</t>
+          <t>2,05; 18,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,93</t>
+          <t>0,0; 47,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,77</t>
+          <t>0,0; 17,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,29</t>
+          <t>0,0; 28,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 20,17</t>
+          <t>1,84; 18,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 10,69</t>
+          <t>2,26; 9,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 17,24</t>
+          <t>4,1; 16,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,54</t>
+          <t>0,0; 32,49</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,37</t>
+          <t>0,0; 29,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 23,85</t>
+          <t>3,35; 23,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 28,66</t>
+          <t>2,97; 30,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,04; 34,21</t>
+          <t>7,08; 34,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,53</t>
+          <t>0,0; 35,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,5</t>
+          <t>0,0; 21,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 41,47</t>
+          <t>5,85; 39,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 21,41</t>
+          <t>2,4; 19,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,66</t>
+          <t>0,0; 22,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 18,31</t>
+          <t>4,26; 18,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 28,17</t>
+          <t>5,36; 27,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 23,73</t>
+          <t>6,39; 23,37</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 40,95</t>
+          <t>5,02; 39,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 28,81</t>
+          <t>4,07; 32,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 25,67</t>
+          <t>3,29; 26,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,12; 27,36</t>
+          <t>6,64; 26,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,75</t>
+          <t>0,0; 19,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 31,49</t>
+          <t>3,95; 31,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 17,77</t>
+          <t>1,57; 16,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 29,58</t>
+          <t>3,34; 28,77</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 20,06</t>
+          <t>3,67; 19,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,84; 22,88</t>
+          <t>3,97; 21,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,16; 20,06</t>
+          <t>6,3; 19,88</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,41</t>
+          <t>0,0; 57,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,18</t>
+          <t>0,0; 35,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,71</t>
+          <t>0,0; 39,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,56; 38,9</t>
+          <t>9,67; 38,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,8</t>
+          <t>0,0; 44,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,38; 31,16</t>
+          <t>3,35; 29,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 23,58</t>
+          <t>6,97; 24,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 38,76</t>
+          <t>4,45; 40,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,3</t>
+          <t>0,0; 10,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,01; 25,89</t>
+          <t>5,03; 27,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,92; 27,64</t>
+          <t>10,98; 27,3</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,49</t>
+          <t>0,0; 30,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,04; 69,02</t>
+          <t>8,85; 68,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,46; 44,07</t>
+          <t>5,4; 42,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,59</t>
+          <t>0,0; 44,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,3</t>
+          <t>0,0; 27,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,72</t>
+          <t>0,0; 16,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,77; 25,35</t>
+          <t>7,88; 26,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,82</t>
+          <t>0,0; 22,66</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 20,71</t>
+          <t>2,32; 19,26</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,89; 26,25</t>
+          <t>2,81; 27,9</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,03; 26,67</t>
+          <t>10,03; 26,56</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,82</t>
+          <t>0,0; 50,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,21</t>
+          <t>0,0; 28,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,48; 45,05</t>
+          <t>5,33; 45,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,77; 39,68</t>
+          <t>10,34; 38,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,32</t>
+          <t>0,0; 35,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,25; 34,22</t>
+          <t>8,32; 30,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,07; 27,74</t>
+          <t>3,14; 26,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,32; 20,79</t>
+          <t>7,34; 20,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,86; 28,16</t>
+          <t>2,84; 27,7</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,76; 25,86</t>
+          <t>8,73; 24,73</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,99; 27,74</t>
+          <t>6,53; 26,83</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,5; 24,49</t>
+          <t>10,04; 23,02</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,29; 21,8</t>
+          <t>8,34; 22,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,39; 12,23</t>
+          <t>5,57; 12,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,22; 16,05</t>
+          <t>7,27; 16,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,21; 22,01</t>
+          <t>11,2; 23,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,86</t>
+          <t>1,89; 12,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,83</t>
+          <t>4,92; 12,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,6; 16,52</t>
+          <t>6,48; 16,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,93; 16,86</t>
+          <t>8,2; 17,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,36; 15,32</t>
+          <t>6,68; 15,4</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,87; 10,68</t>
+          <t>6,04; 10,88</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,95; 14,74</t>
+          <t>8,0; 14,66</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,86; 17,97</t>
+          <t>10,83; 17,61</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, el ingreso en hospital o clínica (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2181; 12196</t>
+          <t>2095; 12888</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1766; 9332</t>
+          <t>1727; 9478</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 7051</t>
+          <t>0; 5837</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3971</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1661</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6515</t>
+          <t>0; 7285</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4730</t>
+          <t>0; 4802</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 11892</t>
+          <t>0; 12036</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2075; 12863</t>
+          <t>2111; 14038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2803; 13501</t>
+          <t>2813; 12918</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>951; 8783</t>
+          <t>951; 8126</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 13933</t>
+          <t>0; 17238</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1003; 10019</t>
+          <t>999; 10563</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1008; 9406</t>
+          <t>983; 8952</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1077; 9007</t>
+          <t>1043; 9170</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 14706</t>
+          <t>0; 12856</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1955</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6377</t>
+          <t>0; 6753</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6417</t>
+          <t>0; 6437</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1772</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>983; 10787</t>
+          <t>982; 9993</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2728; 12868</t>
+          <t>2724; 11920</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2141; 12680</t>
+          <t>3017; 12447</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 13745</t>
+          <t>0; 13724</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4385</t>
+          <t>0; 4392</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1964; 12737</t>
+          <t>1790; 12604</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1044; 10278</t>
+          <t>1065; 10929</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2604; 12659</t>
+          <t>2621; 12699</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4229</t>
+          <t>0; 4744</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6318</t>
+          <t>0; 6236</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1491; 10388</t>
+          <t>1466; 9978</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>681; 6003</t>
+          <t>673; 5401</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6141</t>
+          <t>0; 6364</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3322; 15163</t>
+          <t>3524; 15297</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3147; 17158</t>
+          <t>3263; 16846</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4313; 15433</t>
+          <t>4156; 15199</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>961; 8001</t>
+          <t>981; 7756</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1396; 10416</t>
+          <t>1472; 11660</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>945; 7402</t>
+          <t>949; 7767</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3608; 13869</t>
+          <t>3365; 13526</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1811</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 7261</t>
+          <t>0; 6663</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>951; 7710</t>
+          <t>968; 7607</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>621; 5222</t>
+          <t>461; 4849</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978; 8637</t>
+          <t>977; 8401</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2902; 14268</t>
+          <t>2611; 13544</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2049; 12200</t>
+          <t>2117; 11601</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4933; 16066</t>
+          <t>5047; 15920</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5286</t>
+          <t>0; 5421</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5322</t>
+          <t>0; 4532</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6535</t>
+          <t>0; 5585</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2766; 11255</t>
+          <t>2797; 11110</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4126</t>
+          <t>0; 4384</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2045</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1025; 9459</t>
+          <t>1018; 9037</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2299; 8346</t>
+          <t>2466; 8499</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>859; 7459</t>
+          <t>856; 7734</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 4540</t>
+          <t>0; 5654</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2223; 11482</t>
+          <t>2232; 12025</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7025; 17778</t>
+          <t>7061; 17558</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1423</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4582</t>
+          <t>0; 5336</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>988; 7545</t>
+          <t>967; 7535</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>889; 7177</t>
+          <t>879; 6914</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3973</t>
+          <t>0; 4080</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 6916</t>
+          <t>0; 6887</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5777</t>
+          <t>0; 4966</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2561; 8351</t>
+          <t>2595; 8747</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3142</t>
+          <t>0; 3119</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>971; 8828</t>
+          <t>988; 8209</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1567; 10561</t>
+          <t>1131; 11225</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4939; 13131</t>
+          <t>4938; 13077</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3490</t>
+          <t>0; 2973</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 6435</t>
+          <t>0; 6386</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>833; 6841</t>
+          <t>810; 6878</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2441; 8228</t>
+          <t>2144; 7948</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 6851</t>
+          <t>0; 7994</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5555; 18544</t>
+          <t>4507; 16397</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1231; 11133</t>
+          <t>1259; 10671</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3875; 11007</t>
+          <t>3886; 10847</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>817; 8036</t>
+          <t>810; 7905</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6675; 19709</t>
+          <t>6657; 18849</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3865; 15344</t>
+          <t>3610; 14841</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7739; 18045</t>
+          <t>7400; 16966</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10199; 26830</t>
+          <t>10271; 27270</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15289; 34716</t>
+          <t>15800; 35781</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14421; 32040</t>
+          <t>14519; 32869</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22434; 44043</t>
+          <t>22408; 46561</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1180; 10186</t>
+          <t>1777; 11797</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12527; 30078</t>
+          <t>12509; 31099</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12554; 31425</t>
+          <t>12332; 30864</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>16941; 36007</t>
+          <t>17521; 36713</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>13786; 33224</t>
+          <t>14495; 33396</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>31596; 57467</t>
+          <t>32517; 58572</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>30994; 57455</t>
+          <t>31206; 57173</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>44915; 74353</t>
+          <t>44812; 72856</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$ingresado-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P15D$ingresado-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,21; 38,23</t>
+          <t>6,93; 37,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 15,89</t>
+          <t>2,88; 16,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,27</t>
+          <t>0,0; 13,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,76</t>
+          <t>0,0; 24,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,29</t>
+          <t>0,0; 25,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,4</t>
+          <t>0,0; 57,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 31,69</t>
+          <t>4,53; 29,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 14,31</t>
+          <t>3,29; 13,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 13,05</t>
+          <t>1,51; 13,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,13</t>
+          <t>0,0; 40,73</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 30,24</t>
+          <t>2,84; 28,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,87</t>
+          <t>1,17; 11,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 18,03</t>
+          <t>2,03; 18,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,15</t>
+          <t>0,0; 51,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,76</t>
+          <t>0,0; 16,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,39</t>
+          <t>0,0; 28,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,22 +897,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 18,68</t>
+          <t>1,86; 20,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 9,9</t>
+          <t>2,3; 10,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 16,93</t>
+          <t>2,91; 15,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,49</t>
+          <t>0,0; 36,25</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,42</t>
+          <t>0,0; 35,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 23,6</t>
+          <t>3,36; 24,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 30,48</t>
+          <t>2,89; 31,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,08; 34,32</t>
+          <t>7,06; 32,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,36</t>
+          <t>0,0; 39,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,22</t>
+          <t>0,0; 20,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,85; 39,83</t>
+          <t>5,81; 43,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 19,27</t>
+          <t>2,16; 18,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,45</t>
+          <t>0,0; 21,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,26; 18,48</t>
+          <t>4,2; 18,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 27,66</t>
+          <t>5,76; 27,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,39; 23,37</t>
+          <t>6,15; 22,35</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 39,7</t>
+          <t>5,04; 39,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,07; 32,24</t>
+          <t>3,94; 30,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 26,94</t>
+          <t>0,0; 25,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 26,68</t>
+          <t>7,25; 26,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,04</t>
+          <t>0,0; 18,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 31,07</t>
+          <t>3,89; 32,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 16,5</t>
+          <t>2,14; 17,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 28,77</t>
+          <t>3,36; 27,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 19,04</t>
+          <t>4,28; 20,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 21,76</t>
+          <t>5,42; 23,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 19,88</t>
+          <t>6,63; 19,87</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -1277,27 +1277,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,85</t>
+          <t>0,0; 55,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,08</t>
+          <t>0,0; 41,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,93</t>
+          <t>0,0; 46,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,67; 38,4</t>
+          <t>11,22; 38,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,41</t>
+          <t>0,0; 50,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,35; 29,77</t>
+          <t>3,45; 30,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,97; 24,02</t>
+          <t>6,26; 22,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,45; 40,2</t>
+          <t>4,5; 37,01</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,34</t>
+          <t>0,0; 10,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 27,12</t>
+          <t>4,91; 28,35</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,98; 27,3</t>
+          <t>10,85; 26,85</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,85</t>
+          <t>0,0; 31,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,85; 68,93</t>
+          <t>8,82; 67,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,4; 42,45</t>
+          <t>5,15; 39,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,76</t>
+          <t>0,0; 36,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,19</t>
+          <t>0,0; 23,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,95</t>
+          <t>0,0; 18,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,88; 26,55</t>
+          <t>8,41; 27,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,66</t>
+          <t>0,0; 28,19</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,32; 19,26</t>
+          <t>2,28; 18,84</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,81; 27,9</t>
+          <t>2,75; 26,43</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,03; 26,56</t>
+          <t>9,59; 26,71</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,11</t>
+          <t>0,0; 63,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,99</t>
+          <t>0,0; 29,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,33; 45,3</t>
+          <t>5,48; 45,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,34; 38,33</t>
+          <t>10,42; 39,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,37</t>
+          <t>0,0; 30,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,32; 30,26</t>
+          <t>8,31; 30,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 26,59</t>
+          <t>3,04; 27,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,34; 20,49</t>
+          <t>7,66; 22,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 27,7</t>
+          <t>2,87; 28,77</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,73; 24,73</t>
+          <t>8,6; 25,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,53; 26,83</t>
+          <t>6,56; 27,13</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,04; 23,02</t>
+          <t>10,4; 24,35</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,34; 22,16</t>
+          <t>7,97; 22,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,57; 12,61</t>
+          <t>5,44; 12,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,27; 16,46</t>
+          <t>6,93; 16,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,2; 23,27</t>
+          <t>11,57; 22,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,89; 12,58</t>
+          <t>2,01; 11,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,92; 12,23</t>
+          <t>5,32; 12,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,48; 16,22</t>
+          <t>6,92; 16,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,2; 17,19</t>
+          <t>8,29; 16,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,68; 15,4</t>
+          <t>6,56; 15,27</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,04; 10,88</t>
+          <t>5,99; 10,77</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,0; 14,66</t>
+          <t>8,15; 14,55</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,83; 17,61</t>
+          <t>11,15; 17,78</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3612</t>
         </is>
       </c>
     </row>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2095; 12888</t>
+          <t>2337; 12637</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1727; 9478</t>
+          <t>1715; 9932</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5837</t>
+          <t>0; 5977</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2093,37 +2093,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 7285</t>
+          <t>0; 7451</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4802</t>
+          <t>0; 4656</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 12036</t>
+          <t>0; 12999</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2111; 14038</t>
+          <t>2005; 12990</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2813; 12918</t>
+          <t>2967; 12495</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>951; 8126</t>
+          <t>941; 8360</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 17238</t>
+          <t>0; 17630</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>5518</t>
         </is>
       </c>
     </row>
@@ -2276,22 +2276,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>999; 10563</t>
+          <t>992; 9909</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>983; 8952</t>
+          <t>965; 9588</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1043; 9170</t>
+          <t>1033; 9492</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 12856</t>
+          <t>0; 16964</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6753</t>
+          <t>0; 6332</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6437</t>
+          <t>0; 6534</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2316,22 +2316,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>982; 9993</t>
+          <t>992; 10741</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2724; 11920</t>
+          <t>2762; 12987</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3017; 12447</t>
+          <t>2137; 11452</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 13724</t>
+          <t>0; 17593</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>8850</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4392</t>
+          <t>0; 5306</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1790; 12604</t>
+          <t>1793; 12955</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1065; 10929</t>
+          <t>1038; 11176</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2621; 12699</t>
+          <t>2722; 12642</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4744</t>
+          <t>0; 5320</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6236</t>
+          <t>0; 6091</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1466; 9978</t>
+          <t>1454; 10826</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>673; 5401</t>
+          <t>659; 5734</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6364</t>
+          <t>0; 6118</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3524; 15297</t>
+          <t>3480; 15656</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3263; 16846</t>
+          <t>3507; 16681</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4156; 15199</t>
+          <t>4245; 15428</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>7977</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9495</t>
+          <t>10461</t>
         </is>
       </c>
     </row>
@@ -2692,22 +2692,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>981; 7756</t>
+          <t>984; 7803</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1472; 11660</t>
+          <t>1426; 10949</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>949; 7767</t>
+          <t>0; 7309</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3365; 13526</t>
+          <t>4056; 14560</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2717,37 +2717,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6663</t>
+          <t>0; 6596</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>968; 7607</t>
+          <t>952; 7951</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>461; 4849</t>
+          <t>699; 5832</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977; 8401</t>
+          <t>980; 8042</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2611; 13544</t>
+          <t>3043; 14609</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2117; 11601</t>
+          <t>2890; 12456</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5047; 15920</t>
+          <t>5872; 17595</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>12511</t>
         </is>
       </c>
     </row>
@@ -2900,27 +2900,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5421</t>
+          <t>0; 5200</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4532</t>
+          <t>0; 5396</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5585</t>
+          <t>0; 6537</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2797; 11110</t>
+          <t>3533; 12254</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4384</t>
+          <t>0; 5025</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2930,32 +2930,32 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1018; 9037</t>
+          <t>1048; 9117</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2466; 8499</t>
+          <t>2397; 8500</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>856; 7734</t>
+          <t>867; 7121</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 5654</t>
+          <t>0; 5796</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2232; 12025</t>
+          <t>2175; 12573</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7061; 17558</t>
+          <t>7571; 18741</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>9119</t>
         </is>
       </c>
     </row>
@@ -3113,57 +3113,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5336</t>
+          <t>0; 5484</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>967; 7535</t>
+          <t>964; 7381</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>879; 6914</t>
+          <t>934; 7245</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4080</t>
+          <t>0; 3305</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 6887</t>
+          <t>0; 5949</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4966</t>
+          <t>0; 5382</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2595; 8747</t>
+          <t>3047; 9897</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3119</t>
+          <t>0; 3881</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>988; 8209</t>
+          <t>971; 8033</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1131; 11225</t>
+          <t>1105; 10635</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4938; 13077</t>
+          <t>5211; 14515</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>12843</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2973</t>
+          <t>0; 3796</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 6386</t>
+          <t>0; 6451</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>810; 6878</t>
+          <t>833; 6876</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2144; 7948</t>
+          <t>2399; 9122</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 7994</t>
+          <t>0; 6917</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4507; 16397</t>
+          <t>4501; 16746</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1259; 10671</t>
+          <t>1218; 10850</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3886; 10847</t>
+          <t>4339; 12620</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>810; 7905</t>
+          <t>818; 8209</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6657; 18849</t>
+          <t>6554; 19781</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3610; 14841</t>
+          <t>3631; 15009</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7400; 16966</t>
+          <t>8283; 19398</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32074</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>24002</t>
+          <t>26913</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>56076</t>
+          <t>62913</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10271; 27270</t>
+          <t>9806; 27330</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15800; 35781</t>
+          <t>15444; 35229</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14519; 32869</t>
+          <t>13828; 32443</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22408; 46561</t>
+          <t>25581; 49570</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1777; 11797</t>
+          <t>1882; 10619</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12509; 31099</t>
+          <t>13537; 30608</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12332; 30864</t>
+          <t>13168; 32182</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>17521; 36713</t>
+          <t>19249; 38188</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14495; 33396</t>
+          <t>14220; 33122</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>32517; 58572</t>
+          <t>32220; 57975</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>31206; 57173</t>
+          <t>31789; 56715</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>44812; 72856</t>
+          <t>50546; 80578</t>
         </is>
       </c>
     </row>
